--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/IOWA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/IOWA_2015.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C67">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C503">
